--- a/artfynd/A 43356-2023 artfynd.xlsx
+++ b/artfynd/A 43356-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43356-2023 artfynd.xlsx
+++ b/artfynd/A 43356-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83268859</v>
+        <v>83267705</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505310.0794517847</v>
+        <v>505330</v>
       </c>
       <c r="R2" t="n">
-        <v>6386349.169829789</v>
+        <v>6386341</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,27 +744,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>16C75624-B4C3-42E4-98FF-FC8B758A7D00</t>
+          <t>1BC0A3B0-5924-4562-85B7-DDA63D65BAE9</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +774,230 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>83267706</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Årsås, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>505313</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6386344</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hult</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>707D7BA7-8E14-4A9A-B5CC-9B40580E7484</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2006-06-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2006-06-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83268859</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Årsås, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>505310</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6386349</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hult</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>16C75624-B4C3-42E4-98FF-FC8B758A7D00</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Marielle Gustafsson, Roland Ljunggren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
